--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260717.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260717.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.33%</t>
+          <t>9.90%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.60%</t>
+          <t>9.81%</t>
         </is>
       </c>
     </row>
@@ -660,51 +660,51 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>5.95%</t>
+          <t>5.98%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>183,678,000</t>
+          <t>38,167,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>4.86%</t>
+          <t>4.58%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>38,167,000</t>
+          <t>183,678,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.52%</t>
+          <t>4.54%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.63%</t>
+          <t>3.73%</t>
         </is>
       </c>
     </row>
@@ -743,56 +743,56 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>588,227,000</t>
+          <t>595,227,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.52%</t>
+          <t>3.63%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>202608TX</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>台股期貨</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>2,188</t>
+          <t>25,748,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.31%</t>
+          <t>3.17%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>202608TX</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>台股期貨</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>25,748,000</t>
+          <t>2,101</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>3.07%</t>
         </is>
       </c>
     </row>
@@ -814,90 +814,90 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>2.85%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>95,842,442</t>
+          <t>343,589,964</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>2.81%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>25,514,000</t>
+          <t>130,819,945</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>2.79%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>130,819,945</t>
+          <t>95,842,442</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>2.78%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>28,150,000</t>
+          <t>25,514,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -909,154 +909,154 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>343,589,964</t>
+          <t>193,617,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.65%</t>
+          <t>2.66%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>228,666,516</t>
+          <t>381,325,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.63%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>192,517,000</t>
+          <t>146,652,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.59%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>378,825,000</t>
+          <t>229,866,516</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.56%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>31,686,000</t>
+          <t>133,428,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.54%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>146,652,000</t>
+          <t>28,150,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.52%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>133,428,000</t>
+          <t>31,686,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.50%</t>
         </is>
       </c>
     </row>
@@ -1078,161 +1078,161 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.39%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>61,590,000</t>
+          <t>52,217,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.18%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>51,967,000</t>
+          <t>61,590,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.08%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>80,968,000</t>
+          <t>273,866,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.94%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>188,806,000</t>
+          <t>80,968,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.93%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>上海商銀</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>273,866,000</t>
+          <t>247,525,590</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.92%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>33,600,000</t>
+          <t>188,806,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.89%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>上海商銀</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>245,925,590</t>
+          <t>33,800,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.88%</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>86,399,080</t>
+          <t>86,999,080</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.78%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.68%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>16,870,659,835</t>
+          <t>16,136,791,749</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>3,102,299,800</t>
+          <t>1,759,886,489</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6,700,405</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
